--- a/backend/data/financials_by_company/1026.HK.xlsx
+++ b/backend/data/financials_by_company/1026.HK.xlsx
@@ -662,195 +662,203 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-887500</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.056218</v>
       </c>
       <c r="D2" t="n">
-        <v>-35511000</v>
+        <v>86838000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3550000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-3550000</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-69127000</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>-39102000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>98444000</v>
+      </c>
       <c r="I2" t="n">
-        <v>303554000</v>
+        <v>320151000</v>
       </c>
       <c r="J2" t="n">
-        <v>-39061000</v>
+        <v>86838000</v>
       </c>
       <c r="K2" t="n">
-        <v>-39061000</v>
+        <v>-11606000</v>
       </c>
       <c r="L2" t="n">
-        <v>-29767000</v>
+        <v>-49436000</v>
       </c>
       <c r="M2" t="n">
-        <v>40917000</v>
+        <v>52893000</v>
       </c>
       <c r="N2" t="n">
-        <v>11150000</v>
+        <v>3704000</v>
       </c>
       <c r="O2" t="n">
-        <v>-66464500</v>
+        <v>-39102000</v>
       </c>
       <c r="P2" t="n">
-        <v>-69127000</v>
+        <v>-39102000</v>
       </c>
       <c r="Q2" t="n">
-        <v>373951000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>406000</v>
-      </c>
+        <v>390894000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-39061000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-11359000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5513000000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5513000000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.0071</v>
+      </c>
       <c r="X2" t="n">
-        <v>-69127000</v>
+        <v>-39102000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-69127000</v>
+        <v>-39102000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-69127000</v>
+        <v>-39102000</v>
       </c>
       <c r="AB2" t="n">
-        <v>33625000</v>
+        <v>21771000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-102752000</v>
+        <v>-60873000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-102752000</v>
+        <v>-60873000</v>
       </c>
       <c r="AE2" t="n">
-        <v>22774000</v>
+        <v>-3626000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-79978000</v>
+        <v>-64499000</v>
       </c>
       <c r="AG2" t="n">
-        <v>849000</v>
+        <v>704000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3550000</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>3550000</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-29767000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>-49436000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>247000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>40917000</v>
+        <v>52893000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11150000</v>
+        <v>3704000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-42902000</v>
+        <v>-22393000</v>
       </c>
       <c r="AP2" t="n">
-        <v>70397000</v>
+        <v>70743000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>70397000</v>
+        <v>70893000</v>
       </c>
       <c r="AR2" t="n">
-        <v>70397000</v>
+        <v>70893000</v>
       </c>
       <c r="AS2" t="n">
-        <v>27495000</v>
+        <v>48350000</v>
       </c>
       <c r="AT2" t="n">
-        <v>303554000</v>
+        <v>320151000</v>
       </c>
       <c r="AU2" t="n">
-        <v>331049000</v>
+        <v>368501000</v>
       </c>
       <c r="AV2" t="n">
-        <v>331049000</v>
+        <v>368501000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-4437885.417529</v>
+        <v>-8392500</v>
       </c>
       <c r="C3" t="n">
-        <v>0.062056</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-6028000</v>
+        <v>34394000</v>
       </c>
       <c r="E3" t="n">
-        <v>-60186000</v>
+        <v>-33570000</v>
       </c>
       <c r="F3" t="n">
-        <v>-71514000</v>
+        <v>-33570000</v>
       </c>
       <c r="G3" t="n">
-        <v>-137336000</v>
+        <v>-104068000</v>
       </c>
       <c r="H3" t="n">
-        <v>90822000</v>
+        <v>97734000</v>
       </c>
       <c r="I3" t="n">
-        <v>301376000</v>
+        <v>319643000</v>
       </c>
       <c r="J3" t="n">
-        <v>-66214000</v>
+        <v>824000</v>
       </c>
       <c r="K3" t="n">
-        <v>-157036000</v>
+        <v>-96910000</v>
       </c>
       <c r="L3" t="n">
-        <v>-39517000</v>
+        <v>-45946000</v>
       </c>
       <c r="M3" t="n">
-        <v>48423000</v>
+        <v>53631000</v>
       </c>
       <c r="N3" t="n">
-        <v>9080000</v>
+        <v>7878000</v>
       </c>
       <c r="O3" t="n">
-        <v>-58931885.417529</v>
+        <v>-78890500</v>
       </c>
       <c r="P3" t="n">
-        <v>-137336000</v>
+        <v>-104068000</v>
       </c>
       <c r="Q3" t="n">
-        <v>369263000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>254000</v>
-      </c>
+        <v>403572000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-156862000</v>
+        <v>-96717000</v>
       </c>
       <c r="T3" t="n">
         <v>5513000000</v>
@@ -859,142 +867,144 @@
         <v>5513000000</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0249</v>
+        <v>-0.0189</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0249</v>
+        <v>-0.0189</v>
       </c>
       <c r="X3" t="n">
-        <v>-137336000</v>
+        <v>-104068000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-137336000</v>
+        <v>-104068000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-137336000</v>
+        <v>-104068000</v>
       </c>
       <c r="AB3" t="n">
-        <v>55373000</v>
+        <v>59488000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-192709000</v>
+        <v>-163556000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-192709000</v>
+        <v>-163556000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-12750000</v>
+        <v>13015000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-205459000</v>
+        <v>-150541000</v>
       </c>
       <c r="AG3" t="n">
-        <v>796000</v>
+        <v>2062000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-71514000</v>
+        <v>-33570000</v>
       </c>
       <c r="AI3" t="n">
-        <v>8177000</v>
+        <v>436000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>52009000</v>
+        <v>33134000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-39517000</v>
+        <v>-45946000</v>
       </c>
       <c r="AL3" t="n">
-        <v>174000</v>
+        <v>193000</v>
       </c>
       <c r="AM3" t="n">
-        <v>48423000</v>
+        <v>53631000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9080000</v>
+        <v>7878000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-50116000</v>
+        <v>-54572000</v>
       </c>
       <c r="AP3" t="n">
-        <v>67887000</v>
+        <v>83929000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>67887000</v>
+        <v>84417000</v>
       </c>
       <c r="AR3" t="n">
-        <v>67887000</v>
+        <v>84417000</v>
       </c>
       <c r="AS3" t="n">
-        <v>17771000</v>
+        <v>29357000</v>
       </c>
       <c r="AT3" t="n">
-        <v>301376000</v>
+        <v>319643000</v>
       </c>
       <c r="AU3" t="n">
-        <v>319147000</v>
+        <v>349000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>319147000</v>
+        <v>349000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-8392500</v>
+        <v>-4437885.417529</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.062056</v>
       </c>
       <c r="D4" t="n">
-        <v>34394000</v>
+        <v>-6028000</v>
       </c>
       <c r="E4" t="n">
-        <v>-33570000</v>
+        <v>-60186000</v>
       </c>
       <c r="F4" t="n">
-        <v>-33570000</v>
+        <v>-71514000</v>
       </c>
       <c r="G4" t="n">
-        <v>-104068000</v>
+        <v>-137336000</v>
       </c>
       <c r="H4" t="n">
-        <v>97734000</v>
+        <v>90822000</v>
       </c>
       <c r="I4" t="n">
-        <v>319643000</v>
+        <v>301376000</v>
       </c>
       <c r="J4" t="n">
-        <v>824000</v>
+        <v>-66214000</v>
       </c>
       <c r="K4" t="n">
-        <v>-96910000</v>
+        <v>-157036000</v>
       </c>
       <c r="L4" t="n">
-        <v>-45946000</v>
+        <v>-39517000</v>
       </c>
       <c r="M4" t="n">
-        <v>53631000</v>
+        <v>48423000</v>
       </c>
       <c r="N4" t="n">
-        <v>7878000</v>
+        <v>9080000</v>
       </c>
       <c r="O4" t="n">
-        <v>-78890500</v>
+        <v>-58931885.417529</v>
       </c>
       <c r="P4" t="n">
-        <v>-104068000</v>
+        <v>-137336000</v>
       </c>
       <c r="Q4" t="n">
-        <v>403572000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>369263000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>254000</v>
+      </c>
       <c r="S4" t="n">
-        <v>-96717000</v>
+        <v>-156862000</v>
       </c>
       <c r="T4" t="n">
         <v>5513000000</v>
@@ -1003,229 +1013,219 @@
         <v>5513000000</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0189</v>
+        <v>-0.0249</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0189</v>
+        <v>-0.0249</v>
       </c>
       <c r="X4" t="n">
-        <v>-104068000</v>
+        <v>-137336000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-104068000</v>
+        <v>-137336000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-104068000</v>
+        <v>-137336000</v>
       </c>
       <c r="AB4" t="n">
-        <v>59488000</v>
+        <v>55373000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-163556000</v>
+        <v>-192709000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-163556000</v>
+        <v>-192709000</v>
       </c>
       <c r="AE4" t="n">
-        <v>13015000</v>
+        <v>-12750000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-150541000</v>
+        <v>-205459000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2062000</v>
+        <v>796000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-33570000</v>
+        <v>-71514000</v>
       </c>
       <c r="AI4" t="n">
-        <v>436000</v>
+        <v>8177000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>33134000</v>
+        <v>52009000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-45946000</v>
+        <v>-39517000</v>
       </c>
       <c r="AL4" t="n">
-        <v>193000</v>
+        <v>174000</v>
       </c>
       <c r="AM4" t="n">
-        <v>53631000</v>
+        <v>48423000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7878000</v>
+        <v>9080000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-54572000</v>
+        <v>-50116000</v>
       </c>
       <c r="AP4" t="n">
-        <v>83929000</v>
+        <v>67887000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>84417000</v>
+        <v>67887000</v>
       </c>
       <c r="AR4" t="n">
-        <v>84417000</v>
+        <v>67887000</v>
       </c>
       <c r="AS4" t="n">
-        <v>29357000</v>
+        <v>17771000</v>
       </c>
       <c r="AT4" t="n">
-        <v>319643000</v>
+        <v>301376000</v>
       </c>
       <c r="AU4" t="n">
-        <v>349000000</v>
+        <v>319147000</v>
       </c>
       <c r="AV4" t="n">
-        <v>349000000</v>
+        <v>319147000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-887500</v>
       </c>
       <c r="C5" t="n">
-        <v>0.056218</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>86838000</v>
+        <v>-35511000</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-3550000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-3550000</v>
       </c>
       <c r="G5" t="n">
-        <v>-39102000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>98444000</v>
-      </c>
+        <v>-69127000</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>320151000</v>
+        <v>303554000</v>
       </c>
       <c r="J5" t="n">
-        <v>86838000</v>
+        <v>-39061000</v>
       </c>
       <c r="K5" t="n">
-        <v>-11606000</v>
+        <v>-39061000</v>
       </c>
       <c r="L5" t="n">
-        <v>-49436000</v>
+        <v>-29767000</v>
       </c>
       <c r="M5" t="n">
-        <v>52893000</v>
+        <v>40917000</v>
       </c>
       <c r="N5" t="n">
-        <v>3704000</v>
+        <v>11150000</v>
       </c>
       <c r="O5" t="n">
-        <v>-39102000</v>
+        <v>-66464500</v>
       </c>
       <c r="P5" t="n">
-        <v>-39102000</v>
+        <v>-69127000</v>
       </c>
       <c r="Q5" t="n">
-        <v>390894000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>373951000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>406000</v>
+      </c>
       <c r="S5" t="n">
-        <v>-11359000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>5513000000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5513000000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.0071</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.0071</v>
-      </c>
+        <v>-39061000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-39102000</v>
+        <v>-69127000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-39102000</v>
+        <v>-69127000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-39102000</v>
+        <v>-69127000</v>
       </c>
       <c r="AB5" t="n">
-        <v>21771000</v>
+        <v>33625000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-60873000</v>
+        <v>-102752000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-60873000</v>
+        <v>-102752000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3626000</v>
+        <v>22774000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-64499000</v>
+        <v>-79978000</v>
       </c>
       <c r="AG5" t="n">
-        <v>704000</v>
+        <v>849000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-3550000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3550000</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-49436000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>247000</v>
-      </c>
+        <v>-29767000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>52893000</v>
+        <v>40917000</v>
       </c>
       <c r="AN5" t="n">
-        <v>3704000</v>
+        <v>11150000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-22393000</v>
+        <v>-42902000</v>
       </c>
       <c r="AP5" t="n">
-        <v>70743000</v>
+        <v>70397000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>70893000</v>
+        <v>70397000</v>
       </c>
       <c r="AR5" t="n">
-        <v>70893000</v>
+        <v>70397000</v>
       </c>
       <c r="AS5" t="n">
-        <v>48350000</v>
+        <v>27495000</v>
       </c>
       <c r="AT5" t="n">
-        <v>320151000</v>
+        <v>303554000</v>
       </c>
       <c r="AU5" t="n">
-        <v>368501000</v>
+        <v>331049000</v>
       </c>
       <c r="AV5" t="n">
-        <v>368501000</v>
+        <v>331049000</v>
       </c>
     </row>
   </sheetData>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>5513000000</v>
@@ -1600,46 +1600,46 @@
         <v>5513000000</v>
       </c>
       <c r="D2" t="n">
-        <v>598542000</v>
+        <v>292374000</v>
       </c>
       <c r="E2" t="n">
-        <v>784740000</v>
+        <v>1096919000</v>
       </c>
       <c r="F2" t="n">
-        <v>600824000</v>
+        <v>825398000</v>
       </c>
       <c r="G2" t="n">
-        <v>1452644000</v>
+        <v>2214847000</v>
       </c>
       <c r="H2" t="n">
-        <v>-498227000</v>
+        <v>505889000</v>
       </c>
       <c r="I2" t="n">
-        <v>600824000</v>
+        <v>825398000</v>
       </c>
       <c r="J2" t="n">
-        <v>39875000</v>
+        <v>4913000</v>
       </c>
       <c r="K2" t="n">
-        <v>707779000</v>
+        <v>1122841000</v>
       </c>
       <c r="L2" t="n">
-        <v>1094875000</v>
+        <v>1996998000</v>
       </c>
       <c r="M2" t="n">
-        <v>497440000</v>
+        <v>1319156000</v>
       </c>
       <c r="N2" t="n">
-        <v>-210339000</v>
+        <v>196315000</v>
       </c>
       <c r="O2" t="n">
-        <v>707779000</v>
+        <v>1122841000</v>
       </c>
       <c r="P2" t="n">
-        <v>-8072000</v>
+        <v>-6223000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-612084000</v>
+        <v>-301089000</v>
       </c>
       <c r="R2" t="n">
         <v>1247934000</v>
@@ -1651,143 +1651,155 @@
         <v>55130000</v>
       </c>
       <c r="U2" t="n">
-        <v>1442111000</v>
+        <v>1572300000</v>
       </c>
       <c r="V2" t="n">
-        <v>455303000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1683000</v>
-      </c>
+        <v>929494000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>32198000</v>
+        <v>54929000</v>
       </c>
       <c r="Y2" t="n">
-        <v>421422000</v>
+        <v>874565000</v>
       </c>
       <c r="Z2" t="n">
-        <v>34326000</v>
+        <v>408000</v>
       </c>
       <c r="AA2" t="n">
-        <v>387096000</v>
+        <v>874157000</v>
       </c>
       <c r="AB2" t="n">
-        <v>986808000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>642806000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>122269000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>363318000</v>
+        <v>222354000</v>
       </c>
       <c r="AE2" t="n">
-        <v>5549000</v>
+        <v>4505000</v>
       </c>
       <c r="AF2" t="n">
-        <v>357769000</v>
+        <v>217849000</v>
       </c>
       <c r="AG2" t="n">
-        <v>610761000</v>
+        <v>382657000</v>
       </c>
       <c r="AH2" t="n">
-        <v>133675000</v>
+        <v>97215000</v>
       </c>
       <c r="AI2" t="n">
-        <v>5083000</v>
+        <v>9967000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>472003000</v>
+        <v>275475000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1939551000</v>
+        <v>2891456000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1450970000</v>
+        <v>1742761000</v>
       </c>
       <c r="AM2" t="n">
-        <v>25957000</v>
+        <v>400000</v>
       </c>
       <c r="AN2" t="n">
-        <v>12104000</v>
+        <v>12175000</v>
       </c>
       <c r="AO2" t="n">
-        <v>222954000</v>
+        <v>268172000</v>
       </c>
       <c r="AP2" t="n">
-        <v>222954000</v>
+        <v>268172000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>738924000</v>
+        <v>709387000</v>
       </c>
       <c r="AR2" t="n">
-        <v>106955000</v>
+        <v>297443000</v>
       </c>
       <c r="AS2" t="n">
-        <v>106955000</v>
+        <v>286115000</v>
       </c>
       <c r="AT2" t="n">
+        <v>11328000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>455184000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-262566000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>717750000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>37466000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>621463000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>40258000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>18563000</v>
+      </c>
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="n">
-        <v>344076000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>344076000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>344076000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>488581000</v>
+        <v>1148695000</v>
       </c>
       <c r="BD2" t="n">
-        <v>85350000</v>
+        <v>192441000</v>
       </c>
       <c r="BE2" t="n">
-        <v>2693000</v>
+        <v>3193000</v>
       </c>
       <c r="BF2" t="n">
-        <v>23702000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>3765000</v>
-      </c>
+        <v>16722000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-3396000</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
-        <v>19937000</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
+        <v>19063000</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1055000</v>
+      </c>
       <c r="BK2" t="n">
-        <v>116373000</v>
+        <v>13378000</v>
       </c>
       <c r="BL2" t="n">
-        <v>32453000</v>
+        <v>56691000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-3222000</v>
+        <v>-2815000</v>
       </c>
       <c r="BN2" t="n">
-        <v>35675000</v>
+        <v>59506000</v>
       </c>
       <c r="BO2" t="n">
-        <v>228010000</v>
+        <v>866270000</v>
       </c>
       <c r="BP2" t="n">
-        <v>81687000</v>
+        <v>66638000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>146323000</v>
+        <v>799632000</v>
       </c>
       <c r="BR2" t="n">
-        <v>146323000</v>
+        <v>799632000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>5513000000</v>
@@ -1796,46 +1808,46 @@
         <v>5513000000</v>
       </c>
       <c r="D3" t="n">
-        <v>764028000</v>
+        <v>523164000</v>
       </c>
       <c r="E3" t="n">
-        <v>873185000</v>
+        <v>950328000</v>
       </c>
       <c r="F3" t="n">
-        <v>654434000</v>
+        <v>733709000</v>
       </c>
       <c r="G3" t="n">
-        <v>1666022000</v>
+        <v>1908045000</v>
       </c>
       <c r="H3" t="n">
-        <v>-259801000</v>
+        <v>148015000</v>
       </c>
       <c r="I3" t="n">
-        <v>654434000</v>
+        <v>733709000</v>
       </c>
       <c r="J3" t="n">
-        <v>6387000</v>
+        <v>376000</v>
       </c>
       <c r="K3" t="n">
-        <v>799224000</v>
+        <v>958093000</v>
       </c>
       <c r="L3" t="n">
-        <v>1410047000</v>
+        <v>1706840000</v>
       </c>
       <c r="M3" t="n">
-        <v>613513000</v>
+        <v>1085155000</v>
       </c>
       <c r="N3" t="n">
-        <v>-185711000</v>
+        <v>127062000</v>
       </c>
       <c r="O3" t="n">
-        <v>799224000</v>
+        <v>958093000</v>
       </c>
       <c r="P3" t="n">
-        <v>-6804000</v>
+        <v>-6309000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-542957000</v>
+        <v>-405616000</v>
       </c>
       <c r="R3" t="n">
         <v>1247934000</v>
@@ -1847,153 +1859,153 @@
         <v>55130000</v>
       </c>
       <c r="U3" t="n">
-        <v>1428869000</v>
+        <v>1437012000</v>
       </c>
       <c r="V3" t="n">
-        <v>643772000</v>
+        <v>797167000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>29994000</v>
+        <v>48382000</v>
       </c>
       <c r="Y3" t="n">
-        <v>613778000</v>
+        <v>748785000</v>
       </c>
       <c r="Z3" t="n">
-        <v>2955000</v>
+        <v>38000</v>
       </c>
       <c r="AA3" t="n">
-        <v>610823000</v>
+        <v>748747000</v>
       </c>
       <c r="AB3" t="n">
-        <v>785097000</v>
+        <v>639845000</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>259407000</v>
+        <v>201543000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3432000</v>
+        <v>338000</v>
       </c>
       <c r="AF3" t="n">
-        <v>255975000</v>
+        <v>201205000</v>
       </c>
       <c r="AG3" t="n">
-        <v>485778000</v>
+        <v>398923000</v>
       </c>
       <c r="AH3" t="n">
-        <v>106709000</v>
+        <v>104138000</v>
       </c>
       <c r="AI3" t="n">
-        <v>25620000</v>
+        <v>25068000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>353449000</v>
+        <v>269717000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2042382000</v>
+        <v>2522167000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1517086000</v>
+        <v>1734307000</v>
       </c>
       <c r="AM3" t="n">
-        <v>27002000</v>
+        <v>400000</v>
       </c>
       <c r="AN3" t="n">
-        <v>12373000</v>
+        <v>11358000</v>
       </c>
       <c r="AO3" t="n">
-        <v>232095000</v>
+        <v>244955000</v>
       </c>
       <c r="AP3" t="n">
-        <v>232095000</v>
+        <v>244955000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>762713000</v>
+        <v>854481000</v>
       </c>
       <c r="AR3" t="n">
-        <v>144790000</v>
+        <v>224384000</v>
       </c>
       <c r="AS3" t="n">
-        <v>144790000</v>
+        <v>213056000</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>11328000</v>
       </c>
       <c r="AU3" t="n">
-        <v>338113000</v>
+        <v>398729000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-354716000</v>
+        <v>-296122000</v>
       </c>
       <c r="AW3" t="n">
-        <v>692829000</v>
+        <v>694851000</v>
       </c>
       <c r="AX3" t="n">
-        <v>29545000</v>
+        <v>44957000</v>
       </c>
       <c r="AY3" t="n">
-        <v>600934000</v>
+        <v>595223000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>49467000</v>
+        <v>46364000</v>
       </c>
       <c r="BA3" t="n">
-        <v>12883000</v>
+        <v>8307000</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>525296000</v>
+        <v>787860000</v>
       </c>
       <c r="BD3" t="n">
-        <v>144284000</v>
+        <v>149422000</v>
       </c>
       <c r="BE3" t="n">
-        <v>2587000</v>
+        <v>3156000</v>
       </c>
       <c r="BF3" t="n">
-        <v>19176000</v>
+        <v>14783000</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>-3194000</v>
       </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>18907000</v>
+        <v>17182000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>269000</v>
+        <v>795000</v>
       </c>
       <c r="BK3" t="n">
-        <v>98375000</v>
+        <v>13346000</v>
       </c>
       <c r="BL3" t="n">
-        <v>34472000</v>
+        <v>42659000</v>
       </c>
       <c r="BM3" t="n">
-        <v>-2604000</v>
+        <v>-2619000</v>
       </c>
       <c r="BN3" t="n">
-        <v>37076000</v>
+        <v>45278000</v>
       </c>
       <c r="BO3" t="n">
-        <v>226402000</v>
+        <v>564494000</v>
       </c>
       <c r="BP3" t="n">
-        <v>123632000</v>
+        <v>137706000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>102770000</v>
+        <v>426788000</v>
       </c>
       <c r="BR3" t="n">
-        <v>102770000</v>
+        <v>426788000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>5513000000</v>
@@ -2002,46 +2014,46 @@
         <v>5513000000</v>
       </c>
       <c r="D4" t="n">
-        <v>523164000</v>
+        <v>764028000</v>
       </c>
       <c r="E4" t="n">
-        <v>950328000</v>
+        <v>873185000</v>
       </c>
       <c r="F4" t="n">
-        <v>733709000</v>
+        <v>654434000</v>
       </c>
       <c r="G4" t="n">
-        <v>1908045000</v>
+        <v>1666022000</v>
       </c>
       <c r="H4" t="n">
-        <v>148015000</v>
+        <v>-259801000</v>
       </c>
       <c r="I4" t="n">
-        <v>733709000</v>
+        <v>654434000</v>
       </c>
       <c r="J4" t="n">
-        <v>376000</v>
+        <v>6387000</v>
       </c>
       <c r="K4" t="n">
-        <v>958093000</v>
+        <v>799224000</v>
       </c>
       <c r="L4" t="n">
-        <v>1706840000</v>
+        <v>1410047000</v>
       </c>
       <c r="M4" t="n">
-        <v>1085155000</v>
+        <v>613513000</v>
       </c>
       <c r="N4" t="n">
-        <v>127062000</v>
+        <v>-185711000</v>
       </c>
       <c r="O4" t="n">
-        <v>958093000</v>
+        <v>799224000</v>
       </c>
       <c r="P4" t="n">
-        <v>-6309000</v>
+        <v>-6804000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-405616000</v>
+        <v>-542957000</v>
       </c>
       <c r="R4" t="n">
         <v>1247934000</v>
@@ -2053,153 +2065,153 @@
         <v>55130000</v>
       </c>
       <c r="U4" t="n">
-        <v>1437012000</v>
+        <v>1428869000</v>
       </c>
       <c r="V4" t="n">
-        <v>797167000</v>
+        <v>643772000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>48382000</v>
+        <v>29994000</v>
       </c>
       <c r="Y4" t="n">
-        <v>748785000</v>
+        <v>613778000</v>
       </c>
       <c r="Z4" t="n">
-        <v>38000</v>
+        <v>2955000</v>
       </c>
       <c r="AA4" t="n">
-        <v>748747000</v>
+        <v>610823000</v>
       </c>
       <c r="AB4" t="n">
-        <v>639845000</v>
+        <v>785097000</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>201543000</v>
+        <v>259407000</v>
       </c>
       <c r="AE4" t="n">
-        <v>338000</v>
+        <v>3432000</v>
       </c>
       <c r="AF4" t="n">
-        <v>201205000</v>
+        <v>255975000</v>
       </c>
       <c r="AG4" t="n">
-        <v>398923000</v>
+        <v>485778000</v>
       </c>
       <c r="AH4" t="n">
-        <v>104138000</v>
+        <v>106709000</v>
       </c>
       <c r="AI4" t="n">
-        <v>25068000</v>
+        <v>25620000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>269717000</v>
+        <v>353449000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2522167000</v>
+        <v>2042382000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1734307000</v>
+        <v>1517086000</v>
       </c>
       <c r="AM4" t="n">
-        <v>400000</v>
+        <v>27002000</v>
       </c>
       <c r="AN4" t="n">
-        <v>11358000</v>
+        <v>12373000</v>
       </c>
       <c r="AO4" t="n">
-        <v>244955000</v>
+        <v>232095000</v>
       </c>
       <c r="AP4" t="n">
-        <v>244955000</v>
+        <v>232095000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>854481000</v>
+        <v>762713000</v>
       </c>
       <c r="AR4" t="n">
-        <v>224384000</v>
+        <v>144790000</v>
       </c>
       <c r="AS4" t="n">
-        <v>213056000</v>
+        <v>144790000</v>
       </c>
       <c r="AT4" t="n">
-        <v>11328000</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>398729000</v>
+        <v>338113000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-296122000</v>
+        <v>-354716000</v>
       </c>
       <c r="AW4" t="n">
-        <v>694851000</v>
+        <v>692829000</v>
       </c>
       <c r="AX4" t="n">
-        <v>44957000</v>
+        <v>29545000</v>
       </c>
       <c r="AY4" t="n">
-        <v>595223000</v>
+        <v>600934000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>46364000</v>
+        <v>49467000</v>
       </c>
       <c r="BA4" t="n">
-        <v>8307000</v>
+        <v>12883000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>787860000</v>
+        <v>525296000</v>
       </c>
       <c r="BD4" t="n">
-        <v>149422000</v>
+        <v>144284000</v>
       </c>
       <c r="BE4" t="n">
-        <v>3156000</v>
+        <v>2587000</v>
       </c>
       <c r="BF4" t="n">
-        <v>14783000</v>
+        <v>19176000</v>
       </c>
       <c r="BG4" t="n">
-        <v>-3194000</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="n">
-        <v>17182000</v>
+        <v>18907000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>795000</v>
+        <v>269000</v>
       </c>
       <c r="BK4" t="n">
-        <v>13346000</v>
+        <v>98375000</v>
       </c>
       <c r="BL4" t="n">
-        <v>42659000</v>
+        <v>34472000</v>
       </c>
       <c r="BM4" t="n">
-        <v>-2619000</v>
+        <v>-2604000</v>
       </c>
       <c r="BN4" t="n">
-        <v>45278000</v>
+        <v>37076000</v>
       </c>
       <c r="BO4" t="n">
-        <v>564494000</v>
+        <v>226402000</v>
       </c>
       <c r="BP4" t="n">
-        <v>137706000</v>
+        <v>123632000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>426788000</v>
+        <v>102770000</v>
       </c>
       <c r="BR4" t="n">
-        <v>426788000</v>
+        <v>102770000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>5513000000</v>
@@ -2208,46 +2220,46 @@
         <v>5513000000</v>
       </c>
       <c r="D5" t="n">
-        <v>292374000</v>
+        <v>598542000</v>
       </c>
       <c r="E5" t="n">
-        <v>1096919000</v>
+        <v>784740000</v>
       </c>
       <c r="F5" t="n">
-        <v>825398000</v>
+        <v>600824000</v>
       </c>
       <c r="G5" t="n">
-        <v>2214847000</v>
+        <v>1452644000</v>
       </c>
       <c r="H5" t="n">
-        <v>505889000</v>
+        <v>-498227000</v>
       </c>
       <c r="I5" t="n">
-        <v>825398000</v>
+        <v>600824000</v>
       </c>
       <c r="J5" t="n">
-        <v>4913000</v>
+        <v>39875000</v>
       </c>
       <c r="K5" t="n">
-        <v>1122841000</v>
+        <v>707779000</v>
       </c>
       <c r="L5" t="n">
-        <v>1996998000</v>
+        <v>1094875000</v>
       </c>
       <c r="M5" t="n">
-        <v>1319156000</v>
+        <v>497440000</v>
       </c>
       <c r="N5" t="n">
-        <v>196315000</v>
+        <v>-210339000</v>
       </c>
       <c r="O5" t="n">
-        <v>1122841000</v>
+        <v>707779000</v>
       </c>
       <c r="P5" t="n">
-        <v>-6223000</v>
+        <v>-8072000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-301089000</v>
+        <v>-612084000</v>
       </c>
       <c r="R5" t="n">
         <v>1247934000</v>
@@ -2259,150 +2271,138 @@
         <v>55130000</v>
       </c>
       <c r="U5" t="n">
-        <v>1572300000</v>
+        <v>1442111000</v>
       </c>
       <c r="V5" t="n">
-        <v>929494000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>455303000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1683000</v>
+      </c>
       <c r="X5" t="n">
-        <v>54929000</v>
+        <v>32198000</v>
       </c>
       <c r="Y5" t="n">
-        <v>874565000</v>
+        <v>421422000</v>
       </c>
       <c r="Z5" t="n">
-        <v>408000</v>
+        <v>34326000</v>
       </c>
       <c r="AA5" t="n">
-        <v>874157000</v>
+        <v>387096000</v>
       </c>
       <c r="AB5" t="n">
-        <v>642806000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>122269000</v>
-      </c>
+        <v>986808000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>222354000</v>
+        <v>363318000</v>
       </c>
       <c r="AE5" t="n">
-        <v>4505000</v>
+        <v>5549000</v>
       </c>
       <c r="AF5" t="n">
-        <v>217849000</v>
+        <v>357769000</v>
       </c>
       <c r="AG5" t="n">
-        <v>382657000</v>
+        <v>610761000</v>
       </c>
       <c r="AH5" t="n">
-        <v>97215000</v>
+        <v>133675000</v>
       </c>
       <c r="AI5" t="n">
-        <v>9967000</v>
+        <v>5083000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>275475000</v>
+        <v>472003000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2891456000</v>
+        <v>1939551000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1742761000</v>
+        <v>1450970000</v>
       </c>
       <c r="AM5" t="n">
-        <v>400000</v>
+        <v>25957000</v>
       </c>
       <c r="AN5" t="n">
-        <v>12175000</v>
+        <v>12104000</v>
       </c>
       <c r="AO5" t="n">
-        <v>268172000</v>
+        <v>222954000</v>
       </c>
       <c r="AP5" t="n">
-        <v>268172000</v>
+        <v>222954000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>709387000</v>
+        <v>738924000</v>
       </c>
       <c r="AR5" t="n">
-        <v>297443000</v>
+        <v>106955000</v>
       </c>
       <c r="AS5" t="n">
-        <v>286115000</v>
+        <v>106955000</v>
       </c>
       <c r="AT5" t="n">
-        <v>11328000</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>455184000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-262566000</v>
-      </c>
+        <v>344076000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>717750000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>37466000</v>
-      </c>
+        <v>344076000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>621463000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>40258000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>18563000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
+        <v>344076000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>1148695000</v>
+        <v>488581000</v>
       </c>
       <c r="BD5" t="n">
-        <v>192441000</v>
+        <v>85350000</v>
       </c>
       <c r="BE5" t="n">
-        <v>3193000</v>
+        <v>2693000</v>
       </c>
       <c r="BF5" t="n">
-        <v>16722000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>-3396000</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
+        <v>23702000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="n">
+        <v>3765000</v>
+      </c>
       <c r="BI5" t="n">
-        <v>19063000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1055000</v>
-      </c>
+        <v>19937000</v>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="n">
-        <v>13378000</v>
+        <v>116373000</v>
       </c>
       <c r="BL5" t="n">
-        <v>56691000</v>
+        <v>32453000</v>
       </c>
       <c r="BM5" t="n">
-        <v>-2815000</v>
+        <v>-3222000</v>
       </c>
       <c r="BN5" t="n">
-        <v>59506000</v>
+        <v>35675000</v>
       </c>
       <c r="BO5" t="n">
-        <v>866270000</v>
+        <v>228010000</v>
       </c>
       <c r="BP5" t="n">
-        <v>66638000</v>
+        <v>81687000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>799632000</v>
+        <v>146323000</v>
       </c>
       <c r="BR5" t="n">
-        <v>799632000</v>
+        <v>146323000</v>
       </c>
     </row>
   </sheetData>
@@ -2658,497 +2658,497 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>118019000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>87505000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-646030000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>457705000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-6223000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-41131000</v>
+      </c>
       <c r="G2" t="n">
-        <v>228010000</v>
+        <v>793950000</v>
       </c>
       <c r="H2" t="n">
-        <v>226402000</v>
+        <v>1142675000</v>
       </c>
       <c r="I2" t="n">
-        <v>-3580000</v>
+        <v>24239000</v>
       </c>
       <c r="J2" t="n">
-        <v>5188000</v>
+        <v>-372964000</v>
       </c>
       <c r="K2" t="n">
-        <v>-84664000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>-442723000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-192106000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-52958000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-6223000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-6223000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-188325000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-188325000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-646030000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>457705000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-28167000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>-58877000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-19838000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-19838000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-7660000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-7660000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-31379000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2092000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-33471000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>118019000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+        <v>128636000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-12051000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1992000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>56031000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-8173000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>77062000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-10427000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-978000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1453000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>49189000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>98444000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>52545000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>45899000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-761000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>79000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-64499000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>114262000</v>
+        <v>100544000</v>
       </c>
       <c r="C3" t="n">
-        <v>-190857000</v>
+        <v>-205433000</v>
       </c>
       <c r="D3" t="n">
-        <v>137561000</v>
+        <v>145120000</v>
       </c>
       <c r="E3" t="n">
-        <v>-495000</v>
+        <v>-86000</v>
       </c>
       <c r="F3" t="n">
-        <v>-22645000</v>
+        <v>-47469000</v>
       </c>
       <c r="G3" t="n">
-        <v>226402000</v>
+        <v>561850000</v>
       </c>
       <c r="H3" t="n">
-        <v>561850000</v>
+        <v>793950000</v>
       </c>
       <c r="I3" t="n">
-        <v>-9657000</v>
+        <v>-41275000</v>
       </c>
       <c r="J3" t="n">
-        <v>-325791000</v>
+        <v>-190825000</v>
       </c>
       <c r="K3" t="n">
-        <v>-166190000</v>
+        <v>-94149000</v>
       </c>
       <c r="L3" t="n">
-        <v>-59002000</v>
+        <v>29143000</v>
       </c>
       <c r="M3" t="n">
-        <v>-48615000</v>
+        <v>-54991000</v>
       </c>
       <c r="N3" t="n">
-        <v>-495000</v>
+        <v>-86000</v>
       </c>
       <c r="O3" t="n">
-        <v>-495000</v>
+        <v>-86000</v>
       </c>
       <c r="P3" t="n">
-        <v>-53296000</v>
+        <v>-60313000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-53296000</v>
+        <v>-60313000</v>
       </c>
       <c r="R3" t="n">
-        <v>-190857000</v>
+        <v>-205433000</v>
       </c>
       <c r="S3" t="n">
-        <v>137561000</v>
+        <v>145120000</v>
       </c>
       <c r="T3" t="n">
-        <v>-296508000</v>
+        <v>-244689000</v>
       </c>
       <c r="U3" t="n">
-        <v>-165750000</v>
+        <v>-198100000</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-165750000</v>
+        <v>-198100000</v>
       </c>
       <c r="X3" t="n">
-        <v>-27625000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-27625000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-8868000</v>
+        <v>-9759000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-8868000</v>
+        <v>-9759000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-12620000</v>
+        <v>-36830000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1157000</v>
+        <v>880000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-13777000</v>
+        <v>-37710000</v>
       </c>
       <c r="AF3" t="n">
-        <v>136907000</v>
+        <v>148013000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6629000</v>
+        <v>-13029000</v>
       </c>
       <c r="AH3" t="n">
-        <v>7668000</v>
+        <v>7590000</v>
       </c>
       <c r="AI3" t="n">
-        <v>101759000</v>
+        <v>125393000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11404000</v>
+        <v>93937000</v>
       </c>
       <c r="AK3" t="n">
-        <v>91024000</v>
+        <v>21276000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4273000</v>
+        <v>-809000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-4486000</v>
+        <v>852000</v>
       </c>
       <c r="AN3" t="n">
-        <v>8090000</v>
+        <v>10137000</v>
       </c>
       <c r="AO3" t="n">
-        <v>39343000</v>
+        <v>45753000</v>
       </c>
       <c r="AP3" t="n">
-        <v>90822000</v>
+        <v>97734000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>52444000</v>
+        <v>52825000</v>
       </c>
       <c r="AR3" t="n">
-        <v>38378000</v>
+        <v>44909000</v>
       </c>
       <c r="AS3" t="n">
-        <v>32590000</v>
+        <v>-1260000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1000</v>
+        <v>86000</v>
       </c>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-205459000</v>
+        <v>-150541000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>100544000</v>
+        <v>114262000</v>
       </c>
       <c r="C4" t="n">
-        <v>-205433000</v>
+        <v>-190857000</v>
       </c>
       <c r="D4" t="n">
-        <v>145120000</v>
+        <v>137561000</v>
       </c>
       <c r="E4" t="n">
-        <v>-86000</v>
+        <v>-495000</v>
       </c>
       <c r="F4" t="n">
-        <v>-47469000</v>
+        <v>-22645000</v>
       </c>
       <c r="G4" t="n">
+        <v>226402000</v>
+      </c>
+      <c r="H4" t="n">
         <v>561850000</v>
       </c>
-      <c r="H4" t="n">
-        <v>793950000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-41275000</v>
+        <v>-9657000</v>
       </c>
       <c r="J4" t="n">
-        <v>-190825000</v>
+        <v>-325791000</v>
       </c>
       <c r="K4" t="n">
-        <v>-94149000</v>
+        <v>-166190000</v>
       </c>
       <c r="L4" t="n">
-        <v>29143000</v>
+        <v>-59002000</v>
       </c>
       <c r="M4" t="n">
-        <v>-54991000</v>
+        <v>-48615000</v>
       </c>
       <c r="N4" t="n">
-        <v>-86000</v>
+        <v>-495000</v>
       </c>
       <c r="O4" t="n">
-        <v>-86000</v>
+        <v>-495000</v>
       </c>
       <c r="P4" t="n">
-        <v>-60313000</v>
+        <v>-53296000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-60313000</v>
+        <v>-53296000</v>
       </c>
       <c r="R4" t="n">
-        <v>-205433000</v>
+        <v>-190857000</v>
       </c>
       <c r="S4" t="n">
-        <v>145120000</v>
+        <v>137561000</v>
       </c>
       <c r="T4" t="n">
-        <v>-244689000</v>
+        <v>-296508000</v>
       </c>
       <c r="U4" t="n">
-        <v>-198100000</v>
+        <v>-165750000</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-198100000</v>
+        <v>-165750000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-27625000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-27625000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-9759000</v>
+        <v>-8868000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-9759000</v>
+        <v>-8868000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-36830000</v>
+        <v>-12620000</v>
       </c>
       <c r="AD4" t="n">
-        <v>880000</v>
+        <v>1157000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-37710000</v>
+        <v>-13777000</v>
       </c>
       <c r="AF4" t="n">
-        <v>148013000</v>
+        <v>136907000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-13029000</v>
+        <v>-6629000</v>
       </c>
       <c r="AH4" t="n">
-        <v>7590000</v>
+        <v>7668000</v>
       </c>
       <c r="AI4" t="n">
-        <v>125393000</v>
+        <v>101759000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93937000</v>
+        <v>11404000</v>
       </c>
       <c r="AK4" t="n">
-        <v>21276000</v>
+        <v>91024000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-809000</v>
+        <v>-4273000</v>
       </c>
       <c r="AM4" t="n">
-        <v>852000</v>
+        <v>-4486000</v>
       </c>
       <c r="AN4" t="n">
-        <v>10137000</v>
+        <v>8090000</v>
       </c>
       <c r="AO4" t="n">
-        <v>45753000</v>
+        <v>39343000</v>
       </c>
       <c r="AP4" t="n">
-        <v>97734000</v>
+        <v>90822000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>52825000</v>
+        <v>52444000</v>
       </c>
       <c r="AR4" t="n">
-        <v>44909000</v>
+        <v>38378000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1260000</v>
+        <v>32590000</v>
       </c>
       <c r="AT4" t="n">
-        <v>86000</v>
+        <v>-1000</v>
       </c>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>-150541000</v>
+        <v>-205459000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>87505000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-646030000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>457705000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-6223000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-41131000</v>
-      </c>
+        <v>118019000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>793950000</v>
+        <v>228010000</v>
       </c>
       <c r="H5" t="n">
-        <v>1142675000</v>
+        <v>226402000</v>
       </c>
       <c r="I5" t="n">
-        <v>24239000</v>
+        <v>-3580000</v>
       </c>
       <c r="J5" t="n">
-        <v>-372964000</v>
+        <v>5188000</v>
       </c>
       <c r="K5" t="n">
-        <v>-442723000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-192106000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-52958000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-6223000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-6223000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-188325000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-188325000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-646030000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>457705000</v>
-      </c>
+        <v>-84664000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-58877000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-19838000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-19838000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-7660000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-7660000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-31379000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2092000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-33471000</v>
-      </c>
+        <v>-28167000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>128636000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-12051000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1992000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>56031000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-8173000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>77062000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-10427000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-978000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1453000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>49189000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>98444000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>52545000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>45899000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-761000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>79000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-64499000</v>
-      </c>
+        <v>118019000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3662,182 +3662,182 @@
       </c>
       <c r="CV1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3940,28 +3940,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.089</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.099</v>
+        <v>0.058</v>
       </c>
       <c r="W2" t="n">
-        <v>0.098</v>
+        <v>0.057</v>
       </c>
       <c r="X2" t="n">
-        <v>0.099</v>
+        <v>0.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.089</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.099</v>
+        <v>0.058</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.098</v>
+        <v>0.057</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.099</v>
+        <v>0.06</v>
       </c>
       <c r="AC2" t="n">
         <v>1336089600</v>
@@ -3970,28 +3970,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.392</v>
+        <v>-1.354</v>
       </c>
       <c r="AF2" t="n">
-        <v>520000</v>
+        <v>710000</v>
       </c>
       <c r="AG2" t="n">
-        <v>520000</v>
+        <v>710000</v>
       </c>
       <c r="AH2" t="n">
-        <v>149500</v>
+        <v>155932</v>
       </c>
       <c r="AI2" t="n">
-        <v>79000</v>
+        <v>62000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>79000</v>
+        <v>62000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.076</v>
+        <v>0.056</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.099</v>
+        <v>0.057</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -4000,16 +4000,16 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>490656992</v>
+        <v>314240992</v>
       </c>
       <c r="AP2" t="n">
-        <v>490657000</v>
+        <v>385910000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.067</v>
+        <v>0.057</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.195</v>
+        <v>0.183</v>
       </c>
       <c r="AS2" t="n">
         <v>1.590805</v>
@@ -4018,13 +4018,13 @@
         <v>0.059655</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.693138</v>
+        <v>1.0843693</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.08148</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.104375</v>
+        <v>0.10093</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>654152000</v>
+        <v>477736000</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.44291002</v>
@@ -4065,7 +4065,7 @@
         <v>0.104</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.8557692</v>
+        <v>0.5480769</v>
       </c>
       <c r="BK2" t="n">
         <v>1751241600</v>
@@ -4083,16 +4083,16 @@
         <v>-0.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.257</v>
+        <v>1.649</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-8.205</v>
+        <v>-5.992</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.5435897</v>
+        <v>-0.61748636</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
         <v>0.009943</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.089</v>
+        <v>0.057</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4198,124 +4198,126 @@
           <t>Universal Technologies Holdings Limited</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1004059800000</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>0.057 - 0.06</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>155932</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>0.057 - 0.183</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.6885246</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-61.748634</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1740754418</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1740754418</v>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="DL2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CW2" t="n">
-        <v>1779261185</v>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CY2" t="n">
+      <c r="DM2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>finmb_7655885</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
         <v>0</v>
       </c>
-      <c r="CZ2" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>finmb_7655885</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>1004059800000</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>0.098 - 0.099</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>149500</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.3283582</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0.067 - 0.195</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.10599999</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.5435897</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-54.35897</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1740754418</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1740754418</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>UNIVERSAL TECH</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-18.57143</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.01</v>
+        <v>0.057</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0.00039999932</v>
+        <v>-0.024479996</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.0044742655</v>
+        <v>-0.3004418</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.015374996</v>
+        <v>-0.043929998</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.14730535</v>
+        <v>-0.43525213</v>
       </c>
       <c r="EC2" t="n">
         <v>15</v>
@@ -4323,10 +4325,8 @@
       <c r="ED2" t="n">
         <v>15</v>
       </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>UNIVERSAL TECH</t>
-        </is>
+      <c r="EE2" t="b">
+        <v>0</v>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
